--- a/outputs/q4/q4_resource_coloring.xlsx
+++ b/outputs/q4/q4_resource_coloring.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'运输无人机'!$A$1:$J$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'运输电池'!$A$1:$J$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'中继无人机'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'中继组件'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'中继无人机'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'中继组件'!$A$1:$J$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -517,33 +517,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>A_UAV</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>K2-G1-C-U-01</t>
+          <t>K2-G1-A-U-01</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1626.169077329159</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-009</t>
         </is>
       </c>
     </row>
@@ -563,33 +563,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>A_UAV</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K2-G1-C-U-01</t>
+          <t>K2-G1-A-U-02</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2072.308</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3632.477077329159</v>
+        <v>2422.161333486408</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -619,23 +619,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-01</t>
+          <t>K2-G1-A-U-03</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>32.844</v>
       </c>
       <c r="H4" t="n">
-        <v>1313.47819412363</v>
+        <v>2102.99655401156</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-024</t>
         </is>
       </c>
     </row>
@@ -650,12 +650,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -665,23 +665,23 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-02</t>
+          <t>K2-G1-A-U-04</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1313.479</v>
       </c>
       <c r="H5" t="n">
-        <v>2422.161333486408</v>
+        <v>3970.817647603206</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-020</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -711,23 +711,23 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-03</t>
+          <t>K2-G1-A-U-01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.716</v>
+        <v>1990.41</v>
       </c>
       <c r="H6" t="n">
-        <v>1993.125811655315</v>
+        <v>4000.56255401156</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-016</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -757,14 +757,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-04</t>
+          <t>K2-G1-A-U-03</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>36.247</v>
+        <v>2229.758</v>
       </c>
       <c r="H7" t="n">
-        <v>2106.399554011561</v>
+        <v>4798.851240791447</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-015</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -803,23 +803,23 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-01</t>
+          <t>K2-G1-A-U-02</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1313.479</v>
+        <v>3174.897</v>
       </c>
       <c r="H8" t="n">
-        <v>3970.817647603206</v>
+        <v>5406.905405143679</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-023</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -849,23 +849,23 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-03</t>
+          <t>K2-G1-A-U-01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1993.126</v>
+        <v>4000.563</v>
       </c>
       <c r="H9" t="n">
-        <v>4003.278554011561</v>
+        <v>6430.992780442441</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-007</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -895,23 +895,23 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-04</t>
+          <t>K2-G1-A-U-04</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2277.287</v>
+        <v>4344.632</v>
       </c>
       <c r="H10" t="n">
-        <v>4846.380240791447</v>
+        <v>6947.964416842849</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -941,23 +941,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-02</t>
+          <t>K2-G1-A-U-03</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3177.613</v>
+        <v>5149.607</v>
       </c>
       <c r="H11" t="n">
-        <v>5349.621405143677</v>
+        <v>6838.220231831329</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-004</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -987,23 +987,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-01</t>
+          <t>K2-G1-A-U-02</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4311.047</v>
+        <v>5557.208</v>
       </c>
       <c r="H12" t="n">
-        <v>6914.379416842849</v>
+        <v>6719.230946657878</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
     </row>
@@ -1018,38 +1018,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-03</t>
+          <t>K2-G1-B-U-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4398.57</v>
+        <v>46.776</v>
       </c>
       <c r="H13" t="n">
-        <v>6630.578405143678</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-026</t>
         </is>
       </c>
     </row>
@@ -1064,38 +1064,38 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-04</t>
+          <t>K2-G1-B-U-02</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5152.323</v>
+        <v>46.776</v>
       </c>
       <c r="H14" t="n">
-        <v>7368.13775105334</v>
+        <v>2084.049336451001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
     </row>
@@ -1110,38 +1110,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-02</t>
+          <t>K2-G1-B-U-01</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5390.738</v>
+        <v>2084.05</v>
       </c>
       <c r="H15" t="n">
-        <v>7368.139148248344</v>
+        <v>3840.744300098464</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-012</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1171,14 +1171,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-01</t>
+          <t>K2-G1-B-U-02</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>65.366</v>
+        <v>3007.509</v>
       </c>
       <c r="H16" t="n">
-        <v>1641.641398980425</v>
+        <v>4869.152637063279</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-011</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1217,14 +1217,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-02</t>
+          <t>K2-G1-B-U-01</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>65.366</v>
+        <v>3840.745</v>
       </c>
       <c r="H17" t="n">
-        <v>2102.639336451001</v>
+        <v>5742.57643566033</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-006</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1263,14 +1263,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-01</t>
+          <t>K2-G1-B-U-02</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1641.642</v>
+        <v>4869.153</v>
       </c>
       <c r="H18" t="n">
-        <v>2848.913254843175</v>
+        <v>6830.984435660332</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-003</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1304,23 +1304,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-02</t>
+          <t>K2-G1-C-U-01</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2102.64</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3799.334300098464</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1340,38 +1340,38 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-01</t>
+          <t>K2-G1-C-U-02</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3026.099</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4887.742637063279</v>
+        <v>1626.169077329159</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-022</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-02</t>
+          <t>K2-G1-C-U-01</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4076.107</v>
+        <v>1560.17</v>
       </c>
       <c r="H21" t="n">
-        <v>5283.378254843174</v>
+        <v>3601.982384815261</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
     </row>
@@ -1432,38 +1432,38 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-01</t>
+          <t>K2-G1-C-U-02</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5352.881</v>
+        <v>1815.961</v>
       </c>
       <c r="H22" t="n">
-        <v>7314.712435660331</v>
+        <v>4187.119530475286</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-025</t>
         </is>
       </c>
     </row>
@@ -1478,38 +1478,38 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-02</t>
+          <t>K2-G1-C-U-01</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5443.594</v>
+        <v>3601.983</v>
       </c>
       <c r="H23" t="n">
-        <v>7345.425435660331</v>
+        <v>6183.72363369963</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1539,23 +1539,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>K2-G2-C-U-01</t>
+          <t>K2-G1-C-U-02</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>30.495</v>
+        <v>4291.262</v>
       </c>
       <c r="H24" t="n">
-        <v>2072.307384815261</v>
+        <v>6727.353349604668</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-008</t>
         </is>
       </c>
     </row>
@@ -1575,33 +1575,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>A_UAV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>K2-G2-C-U-02</t>
+          <t>K2-G2-A-U-01</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1626.17</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3997.328530475288</v>
+        <v>1313.47819412363</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-001</t>
         </is>
       </c>
     </row>
@@ -1621,33 +1621,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>K2-G2-C-U-01</t>
+          <t>K2-G2-B-U-01</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3642.85</v>
+        <v>1623.052</v>
       </c>
       <c r="H26" t="n">
-        <v>6224.590633699631</v>
+        <v>2830.323254843175</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-002</t>
         </is>
       </c>
     </row>
@@ -1667,33 +1667,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>K2-G2-C-U-02</t>
+          <t>K2-G2-B-U-01</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4530.417</v>
+        <v>5742.577</v>
       </c>
       <c r="H27" t="n">
-        <v>6966.508349604669</v>
+        <v>6949.848254843174</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-017</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1730,16 +1730,16 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1626.169077329159</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-005</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1769,23 +1769,23 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>K3-G1-C-U-01</t>
+          <t>K3-G1-C-U-02</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2072.308</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3632.477077329159</v>
+        <v>1626.169077329159</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-022</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2422.161333486408</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-009</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2.716</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1993.125811655315</v>
+        <v>2422.161333486408</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-014</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>36.247</v>
+        <v>32.844</v>
       </c>
       <c r="H32" t="n">
-        <v>2106.399554011561</v>
+        <v>2102.99655401156</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-024</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-020</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1999,23 +1999,23 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>K3-G2-A-U-02</t>
+          <t>K3-G2-A-U-01</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1993.126</v>
+        <v>1990.41</v>
       </c>
       <c r="H34" t="n">
-        <v>4003.278554011561</v>
+        <v>4000.56255401156</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-016</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2277.287</v>
+        <v>2229.758</v>
       </c>
       <c r="H35" t="n">
-        <v>4846.380240791447</v>
+        <v>4798.851240791447</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-015</t>
         </is>
       </c>
     </row>
@@ -2091,18 +2091,18 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>K3-G2-A-U-01</t>
+          <t>K3-G2-A-U-02</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3177.613</v>
+        <v>3174.897</v>
       </c>
       <c r="H36" t="n">
-        <v>5349.621405143677</v>
+        <v>5406.905405143679</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2137,23 +2137,23 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>K3-G2-A-U-02</t>
+          <t>K3-G2-A-U-01</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4311.047</v>
+        <v>4000.563</v>
       </c>
       <c r="H37" t="n">
-        <v>6914.379416842849</v>
+        <v>6430.992780442441</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-007</t>
         </is>
       </c>
     </row>
@@ -2187,14 +2187,14 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4398.57</v>
+        <v>4344.632</v>
       </c>
       <c r="H38" t="n">
-        <v>6630.578405143678</v>
+        <v>6947.964416842849</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5152.323</v>
+        <v>5149.607</v>
       </c>
       <c r="H39" t="n">
-        <v>7368.13775105334</v>
+        <v>6838.220231831329</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-004</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2275,23 +2275,23 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>K3-G2-A-U-01</t>
+          <t>K3-G2-A-U-02</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5390.738</v>
+        <v>5557.208</v>
       </c>
       <c r="H40" t="n">
-        <v>7368.139148248344</v>
+        <v>6719.230946657878</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-013</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="H41" t="n">
-        <v>1641.641398980425</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-026</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="H42" t="n">
-        <v>2102.639336451001</v>
+        <v>2084.049336451001</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-019</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2102.64</v>
+        <v>2084.05</v>
       </c>
       <c r="H43" t="n">
-        <v>3799.334300098464</v>
+        <v>3840.744300098464</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-012</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3026.099</v>
+        <v>3007.509</v>
       </c>
       <c r="H44" t="n">
-        <v>4887.742637063279</v>
+        <v>4869.152637063279</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-011</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>5352.881</v>
+        <v>3840.745</v>
       </c>
       <c r="H45" t="n">
-        <v>7314.712435660331</v>
+        <v>5742.57643566033</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>5443.594</v>
+        <v>4869.153</v>
       </c>
       <c r="H46" t="n">
-        <v>7345.425435660331</v>
+        <v>6830.984435660332</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-003</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>30.495</v>
+        <v>1560.17</v>
       </c>
       <c r="H47" t="n">
-        <v>2072.307384815261</v>
+        <v>3601.982384815261</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-021</t>
         </is>
       </c>
     </row>
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1626.17</v>
+        <v>1815.961</v>
       </c>
       <c r="H48" t="n">
-        <v>3997.328530475288</v>
+        <v>4187.119530475286</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3642.85</v>
+        <v>3601.983</v>
       </c>
       <c r="H49" t="n">
-        <v>6224.590633699631</v>
+        <v>6183.72363369963</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>4530.417</v>
+        <v>4291.262</v>
       </c>
       <c r="H50" t="n">
-        <v>6966.508349604669</v>
+        <v>6727.353349604668</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-008</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-001</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1641.642</v>
+        <v>1623.052</v>
       </c>
       <c r="H52" t="n">
-        <v>2848.913254843175</v>
+        <v>2830.323254843175</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-002</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4076.107</v>
+        <v>5742.577</v>
       </c>
       <c r="H53" t="n">
-        <v>5283.378254843174</v>
+        <v>6949.848254843174</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-017</t>
         </is>
       </c>
     </row>
@@ -2909,33 +2909,33 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>A_UAV</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>K2-G1-C-U-01</t>
+          <t>K2-G1-A-U-01</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1626.169077329159</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-009</t>
         </is>
       </c>
     </row>
@@ -2955,33 +2955,33 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>A_UAV</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>K2-G1-C-U-01</t>
+          <t>K2-G1-A-U-02</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2072.308</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>3632.477077329159</v>
+        <v>2422.161333486408</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3011,23 +3011,23 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-01</t>
+          <t>K2-G1-A-U-03</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>32.844</v>
       </c>
       <c r="H56" t="n">
-        <v>1313.47819412363</v>
+        <v>2102.99655401156</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-024</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3057,23 +3057,23 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-02</t>
+          <t>K2-G1-A-U-04</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1313.479</v>
       </c>
       <c r="H57" t="n">
-        <v>2422.161333486408</v>
+        <v>3970.817647603206</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-020</t>
         </is>
       </c>
     </row>
@@ -3088,12 +3088,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3103,23 +3103,23 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-03</t>
+          <t>K2-G1-A-U-01</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2.716</v>
+        <v>1990.41</v>
       </c>
       <c r="H58" t="n">
-        <v>1993.125811655315</v>
+        <v>4000.56255401156</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-016</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3149,14 +3149,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-04</t>
+          <t>K2-G1-A-U-03</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>36.247</v>
+        <v>2229.758</v>
       </c>
       <c r="H59" t="n">
-        <v>2106.399554011561</v>
+        <v>4798.851240791447</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-015</t>
         </is>
       </c>
     </row>
@@ -3180,12 +3180,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3195,23 +3195,23 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-01</t>
+          <t>K2-G1-A-U-02</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1313.479</v>
+        <v>3174.897</v>
       </c>
       <c r="H60" t="n">
-        <v>3970.817647603206</v>
+        <v>5406.905405143679</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-023</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3241,23 +3241,23 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-03</t>
+          <t>K2-G1-A-U-01</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1993.126</v>
+        <v>4000.563</v>
       </c>
       <c r="H61" t="n">
-        <v>4003.278554011561</v>
+        <v>6430.992780442441</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-007</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3272,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3287,23 +3287,23 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-04</t>
+          <t>K2-G1-A-U-04</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2277.287</v>
+        <v>4344.632</v>
       </c>
       <c r="H62" t="n">
-        <v>4846.380240791447</v>
+        <v>6947.964416842849</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
     </row>
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3333,23 +3333,23 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-02</t>
+          <t>K2-G1-A-U-03</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3177.613</v>
+        <v>5149.607</v>
       </c>
       <c r="H63" t="n">
-        <v>5349.621405143677</v>
+        <v>6838.220231831329</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-004</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3379,23 +3379,23 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-01</t>
+          <t>K2-G1-A-U-02</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>4311.047</v>
+        <v>5557.208</v>
       </c>
       <c r="H64" t="n">
-        <v>6914.379416842849</v>
+        <v>6719.230946657878</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
     </row>
@@ -3410,38 +3410,38 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>A_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-03</t>
+          <t>K2-G1-B-U-01</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>4398.57</v>
+        <v>46.776</v>
       </c>
       <c r="H65" t="n">
-        <v>6630.578405143678</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-026</t>
         </is>
       </c>
     </row>
@@ -3456,38 +3456,38 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>A_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-04</t>
+          <t>K2-G1-B-U-02</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>5152.323</v>
+        <v>46.776</v>
       </c>
       <c r="H66" t="n">
-        <v>7368.13775105334</v>
+        <v>2084.049336451001</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
     </row>
@@ -3502,38 +3502,38 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>A_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>K2-G2-A-U-02</t>
+          <t>K2-G1-B-U-01</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>5390.738</v>
+        <v>2084.05</v>
       </c>
       <c r="H67" t="n">
-        <v>7368.139148248344</v>
+        <v>3840.744300098464</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-012</t>
         </is>
       </c>
     </row>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3563,14 +3563,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-01</t>
+          <t>K2-G1-B-U-02</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>65.366</v>
+        <v>3007.509</v>
       </c>
       <c r="H68" t="n">
-        <v>1641.641398980425</v>
+        <v>4869.152637063279</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-011</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3609,14 +3609,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-02</t>
+          <t>K2-G1-B-U-01</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>65.366</v>
+        <v>3840.745</v>
       </c>
       <c r="H69" t="n">
-        <v>2102.639336451001</v>
+        <v>5742.57643566033</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-006</t>
         </is>
       </c>
     </row>
@@ -3640,12 +3640,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3655,14 +3655,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-01</t>
+          <t>K2-G1-B-U-02</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1641.642</v>
+        <v>4869.153</v>
       </c>
       <c r="H70" t="n">
-        <v>2848.913254843175</v>
+        <v>6830.984435660332</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-003</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3696,23 +3696,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-02</t>
+          <t>K2-G1-C-U-01</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2102.64</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>3799.334300098464</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3732,38 +3732,38 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-01</t>
+          <t>K2-G1-C-U-02</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3026.099</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>4887.742637063279</v>
+        <v>1626.169077329159</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-022</t>
         </is>
       </c>
     </row>
@@ -3778,38 +3778,38 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-02</t>
+          <t>K2-G1-C-U-01</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>4076.107</v>
+        <v>1560.17</v>
       </c>
       <c r="H73" t="n">
-        <v>5283.378254843174</v>
+        <v>3601.982384815261</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
     </row>
@@ -3824,38 +3824,38 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-01</t>
+          <t>K2-G1-C-U-02</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>5352.881</v>
+        <v>1815.961</v>
       </c>
       <c r="H74" t="n">
-        <v>7314.712435660331</v>
+        <v>4187.119530475286</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-025</t>
         </is>
       </c>
     </row>
@@ -3870,38 +3870,38 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>B_UAV</t>
+          <t>C_UAV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>K2-G2-B-U-02</t>
+          <t>K2-G1-C-U-01</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>5443.594</v>
+        <v>3601.983</v>
       </c>
       <c r="H75" t="n">
-        <v>7345.425435660331</v>
+        <v>6183.72363369963</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3931,23 +3931,23 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>K2-G2-C-U-01</t>
+          <t>K2-G1-C-U-02</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>30.495</v>
+        <v>4291.262</v>
       </c>
       <c r="H76" t="n">
-        <v>2072.307384815261</v>
+        <v>6727.353349604668</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-008</t>
         </is>
       </c>
     </row>
@@ -3967,33 +3967,33 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>A_UAV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>K2-G2-C-U-02</t>
+          <t>K2-G2-A-U-01</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1626.17</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>3997.328530475288</v>
+        <v>1313.47819412363</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-001</t>
         </is>
       </c>
     </row>
@@ -4013,33 +4013,33 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>K2-G2-C-U-01</t>
+          <t>K2-G2-B-U-01</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>3642.85</v>
+        <v>1623.052</v>
       </c>
       <c r="H78" t="n">
-        <v>6224.590633699631</v>
+        <v>2830.323254843175</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-002</t>
         </is>
       </c>
     </row>
@@ -4059,33 +4059,33 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>C_UAV</t>
+          <t>B_UAV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>K2-G2-C-U-02</t>
+          <t>K2-G2-B-U-01</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>4530.417</v>
+        <v>5742.577</v>
       </c>
       <c r="H79" t="n">
-        <v>6966.508349604669</v>
+        <v>6949.848254843174</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-017</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4122,16 +4122,16 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1626.169077329159</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-005</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4161,23 +4161,23 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>K3-G1-C-U-01</t>
+          <t>K3-G1-C-U-02</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2072.308</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>3632.477077329159</v>
+        <v>1626.169077329159</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-022</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>2422.161333486408</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-009</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2.716</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1993.125811655315</v>
+        <v>2422.161333486408</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-014</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>36.247</v>
+        <v>32.844</v>
       </c>
       <c r="H84" t="n">
-        <v>2106.399554011561</v>
+        <v>2102.99655401156</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-024</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-020</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4391,23 +4391,23 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>K3-G2-A-U-02</t>
+          <t>K3-G2-A-U-01</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1993.126</v>
+        <v>1990.41</v>
       </c>
       <c r="H86" t="n">
-        <v>4003.278554011561</v>
+        <v>4000.56255401156</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-016</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2277.287</v>
+        <v>2229.758</v>
       </c>
       <c r="H87" t="n">
-        <v>4846.380240791447</v>
+        <v>4798.851240791447</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-015</t>
         </is>
       </c>
     </row>
@@ -4483,18 +4483,18 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>K3-G2-A-U-01</t>
+          <t>K3-G2-A-U-02</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>3177.613</v>
+        <v>3174.897</v>
       </c>
       <c r="H88" t="n">
-        <v>5349.621405143677</v>
+        <v>5406.905405143679</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4529,23 +4529,23 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>K3-G2-A-U-02</t>
+          <t>K3-G2-A-U-01</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>4311.047</v>
+        <v>4000.563</v>
       </c>
       <c r="H89" t="n">
-        <v>6914.379416842849</v>
+        <v>6430.992780442441</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-007</t>
         </is>
       </c>
     </row>
@@ -4579,14 +4579,14 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>4398.57</v>
+        <v>4344.632</v>
       </c>
       <c r="H90" t="n">
-        <v>6630.578405143678</v>
+        <v>6947.964416842849</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>5152.323</v>
+        <v>5149.607</v>
       </c>
       <c r="H91" t="n">
-        <v>7368.13775105334</v>
+        <v>6838.220231831329</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-004</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4667,23 +4667,23 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>K3-G2-A-U-01</t>
+          <t>K3-G2-A-U-02</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>5390.738</v>
+        <v>5557.208</v>
       </c>
       <c r="H92" t="n">
-        <v>7368.139148248344</v>
+        <v>6719.230946657878</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-013</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="H93" t="n">
-        <v>1641.641398980425</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-026</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="H94" t="n">
-        <v>2102.639336451001</v>
+        <v>2084.049336451001</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-019</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2102.64</v>
+        <v>2084.05</v>
       </c>
       <c r="H95" t="n">
-        <v>3799.334300098464</v>
+        <v>3840.744300098464</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-012</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>3026.099</v>
+        <v>3007.509</v>
       </c>
       <c r="H96" t="n">
-        <v>4887.742637063279</v>
+        <v>4869.152637063279</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-011</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>5352.881</v>
+        <v>3840.745</v>
       </c>
       <c r="H97" t="n">
-        <v>7314.712435660331</v>
+        <v>5742.57643566033</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>5443.594</v>
+        <v>4869.153</v>
       </c>
       <c r="H98" t="n">
-        <v>7345.425435660331</v>
+        <v>6830.984435660332</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-003</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>30.495</v>
+        <v>1560.17</v>
       </c>
       <c r="H99" t="n">
-        <v>2072.307384815261</v>
+        <v>3601.982384815261</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-021</t>
         </is>
       </c>
     </row>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1626.17</v>
+        <v>1815.961</v>
       </c>
       <c r="H100" t="n">
-        <v>3997.328530475288</v>
+        <v>4187.119530475286</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>3642.85</v>
+        <v>3601.983</v>
       </c>
       <c r="H101" t="n">
-        <v>6224.590633699631</v>
+        <v>6183.72363369963</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>4530.417</v>
+        <v>4291.262</v>
       </c>
       <c r="H102" t="n">
-        <v>6966.508349604669</v>
+        <v>6727.353349604668</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-008</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-001</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1641.642</v>
+        <v>1623.052</v>
       </c>
       <c r="H104" t="n">
-        <v>2848.913254843175</v>
+        <v>2830.323254843175</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-002</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>4076.107</v>
+        <v>5742.577</v>
       </c>
       <c r="H105" t="n">
-        <v>5283.378254843174</v>
+        <v>6949.848254843174</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-017</t>
         </is>
       </c>
     </row>
@@ -5380,33 +5380,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>A_battery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>K2-G1-C-BAT-01</t>
+          <t>K2-G1-A-BAT-01</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3239.784571192919</v>
+        <v>3174.895936577519</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-009</t>
         </is>
       </c>
     </row>
@@ -5426,33 +5426,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>A_battery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K2-G1-C-BAT-02</t>
+          <t>K2-G1-A-BAT-02</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2072.308</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5288.51014937907</v>
+        <v>3779.947033441976</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
     </row>
@@ -5467,12 +5467,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5482,23 +5482,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-01</t>
+          <t>K2-G1-A-BAT-03</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>32.844</v>
       </c>
       <c r="H4" t="n">
-        <v>2192.366042252357</v>
+        <v>3274.434434614842</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-024</t>
         </is>
       </c>
     </row>
@@ -5513,12 +5513,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5528,23 +5528,23 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-02</t>
+          <t>K2-G1-A-BAT-04</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1313.479</v>
       </c>
       <c r="H5" t="n">
-        <v>3779.947033441976</v>
+        <v>5390.737354551678</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-020</t>
         </is>
       </c>
     </row>
@@ -5559,12 +5559,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5574,23 +5574,23 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-03</t>
+          <t>K2-G1-A-BAT-05</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.716</v>
+        <v>1990.41</v>
       </c>
       <c r="H6" t="n">
-        <v>3177.611936577518</v>
+        <v>5149.606026117086</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-016</t>
         </is>
       </c>
     </row>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5620,23 +5620,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-04</t>
+          <t>K2-G1-A-BAT-06</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>36.247</v>
+        <v>2229.758</v>
       </c>
       <c r="H7" t="n">
-        <v>3277.837434614842</v>
+        <v>6323.116552585012</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-015</t>
         </is>
       </c>
     </row>
@@ -5651,12 +5651,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5666,23 +5666,23 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-05</t>
+          <t>K2-G1-A-BAT-01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1313.479</v>
+        <v>3174.897</v>
       </c>
       <c r="H8" t="n">
-        <v>5390.737354551678</v>
+        <v>6721.949810986717</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-023</t>
         </is>
       </c>
     </row>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5712,23 +5712,23 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-06</t>
+          <t>K2-G1-A-BAT-02</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1993.126</v>
+        <v>4000.563</v>
       </c>
       <c r="H9" t="n">
-        <v>5152.322026117086</v>
+        <v>7808.561614873621</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-007</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5758,23 +5758,23 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-01</t>
+          <t>K2-G1-A-BAT-03</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2277.287</v>
+        <v>4344.632</v>
       </c>
       <c r="H10" t="n">
-        <v>6370.645552585012</v>
+        <v>8418.803815705602</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5804,23 +5804,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-03</t>
+          <t>K2-G1-A-BAT-05</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3177.613</v>
+        <v>5149.607</v>
       </c>
       <c r="H11" t="n">
-        <v>6657.343227715388</v>
+        <v>8011.704299881098</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-004</t>
         </is>
       </c>
     </row>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5850,14 +5850,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-02</t>
+          <t>K2-G1-A-BAT-04</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4311.047</v>
+        <v>5557.208</v>
       </c>
       <c r="H12" t="n">
-        <v>8385.218815705603</v>
+        <v>7546.392154794932</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
     </row>
@@ -5881,38 +5881,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-04</t>
+          <t>K2-G1-B-BAT-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4398.57</v>
+        <v>46.776</v>
       </c>
       <c r="H13" t="n">
-        <v>7945.622810986716</v>
+        <v>3007.507809356639</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-026</t>
         </is>
       </c>
     </row>
@@ -5927,38 +5927,38 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-06</t>
+          <t>K2-G1-B-BAT-02</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5152.323</v>
+        <v>46.776</v>
       </c>
       <c r="H14" t="n">
-        <v>8733.773213282222</v>
+        <v>3736.465649755144</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
     </row>
@@ -5973,38 +5973,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-05</t>
+          <t>K2-G1-B-BAT-03</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5390.738</v>
+        <v>2084.05</v>
       </c>
       <c r="H15" t="n">
-        <v>8480.457322337608</v>
+        <v>5550.5346802819</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-012</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6034,23 +6034,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-01</t>
+          <t>K2-G1-B-BAT-01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>65.366</v>
+        <v>3007.509</v>
       </c>
       <c r="H16" t="n">
-        <v>3026.097809356639</v>
+        <v>6619.69696700587</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-011</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6080,23 +6080,23 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-02</t>
+          <t>K2-G1-B-BAT-02</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>65.366</v>
+        <v>3840.745</v>
       </c>
       <c r="H17" t="n">
-        <v>3755.055649755144</v>
+        <v>7606.718926283403</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-006</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6126,23 +6126,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-03</t>
+          <t>K2-G1-B-BAT-04</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1641.642</v>
+        <v>4869.153</v>
       </c>
       <c r="H18" t="n">
-        <v>4076.105873047899</v>
+        <v>8786.895523772557</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-003</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6167,23 +6167,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-04</t>
+          <t>K2-G1-C-BAT-01</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2102.64</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5443.59246446922</v>
+        <v>3216.20214937907</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -6203,38 +6203,38 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-01</t>
+          <t>K2-G1-C-BAT-02</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3026.099</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6638.28696700587</v>
+        <v>3239.784571192919</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-022</t>
         </is>
       </c>
     </row>
@@ -6249,38 +6249,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-02</t>
+          <t>K2-G1-C-BAT-03</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4076.107</v>
+        <v>1560.17</v>
       </c>
       <c r="H21" t="n">
-        <v>6412.084416558292</v>
+        <v>6060.090759184022</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
     </row>
@@ -6295,38 +6295,38 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-03</t>
+          <t>K2-G1-C-BAT-04</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5352.881</v>
+        <v>1815.961</v>
       </c>
       <c r="H22" t="n">
-        <v>9270.623523772556</v>
+        <v>6441.860943323286</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-025</t>
         </is>
       </c>
     </row>
@@ -6341,38 +6341,38 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-04</t>
+          <t>K2-G1-C-BAT-01</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5443.594</v>
+        <v>3601.983</v>
       </c>
       <c r="H23" t="n">
-        <v>9209.567926283402</v>
+        <v>8602.25309044097</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
     </row>
@@ -6387,12 +6387,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -6402,23 +6402,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>K2-G2-C-BAT-01</t>
+          <t>K2-G1-C-BAT-02</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>30.495</v>
+        <v>4291.262</v>
       </c>
       <c r="H24" t="n">
-        <v>4530.415759184022</v>
+        <v>9226.144509758493</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-008</t>
         </is>
       </c>
     </row>
@@ -6438,33 +6438,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>A_battery</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>K2-G2-C-BAT-02</t>
+          <t>K2-G2-A-BAT-01</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1626.17</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6285.291989402955</v>
+        <v>2192.366042252357</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-001</t>
         </is>
       </c>
     </row>
@@ -6484,33 +6484,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>K2-G2-C-BAT-03</t>
+          <t>K2-G2-B-BAT-01</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3642.85</v>
+        <v>1623.052</v>
       </c>
       <c r="H26" t="n">
-        <v>8739.717663171208</v>
+        <v>4057.515873047899</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-002</t>
         </is>
       </c>
     </row>
@@ -6530,33 +6530,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>K2-G2-C-BAT-01</t>
+          <t>K2-G2-B-BAT-01</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4530.417</v>
+        <v>5742.577</v>
       </c>
       <c r="H27" t="n">
-        <v>9465.299509758494</v>
+        <v>8078.554416558292</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-017</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6593,16 +6593,16 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3239.784571192919</v>
+        <v>3216.20214937907</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-005</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6636,19 +6636,19 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2072.308</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5288.51014937907</v>
+        <v>3239.784571192919</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-022</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6685,16 +6685,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3779.947033441976</v>
+        <v>3174.895936577519</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-009</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6728,19 +6728,19 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2.716</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3177.611936577518</v>
+        <v>3779.947033441976</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-014</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6774,19 +6774,19 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>36.247</v>
+        <v>32.844</v>
       </c>
       <c r="H32" t="n">
-        <v>3277.837434614842</v>
+        <v>3274.434434614842</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-024</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-020</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6866,19 +6866,19 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1993.126</v>
+        <v>1990.41</v>
       </c>
       <c r="H34" t="n">
-        <v>5152.322026117086</v>
+        <v>5149.606026117086</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-016</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6912,19 +6912,19 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2277.287</v>
+        <v>2229.758</v>
       </c>
       <c r="H35" t="n">
-        <v>6370.645552585012</v>
+        <v>6323.116552585012</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-015</t>
         </is>
       </c>
     </row>
@@ -6954,18 +6954,18 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>K3-G2-A-BAT-02</t>
+          <t>K3-G2-A-BAT-01</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3177.613</v>
+        <v>3174.897</v>
       </c>
       <c r="H36" t="n">
-        <v>6657.343227715388</v>
+        <v>6721.949810986717</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -7000,23 +7000,23 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>K3-G2-A-BAT-01</t>
+          <t>K3-G2-A-BAT-02</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4311.047</v>
+        <v>4000.563</v>
       </c>
       <c r="H37" t="n">
-        <v>8385.218815705603</v>
+        <v>7808.561614873621</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-007</t>
         </is>
       </c>
     </row>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4398.57</v>
+        <v>4344.632</v>
       </c>
       <c r="H38" t="n">
-        <v>7945.622810986716</v>
+        <v>8418.803815705602</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -7096,19 +7096,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5152.323</v>
+        <v>5149.607</v>
       </c>
       <c r="H39" t="n">
-        <v>8733.773213282222</v>
+        <v>8011.704299881098</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-004</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -7142,19 +7142,19 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5390.738</v>
+        <v>5557.208</v>
       </c>
       <c r="H40" t="n">
-        <v>8480.457322337608</v>
+        <v>7546.392154794932</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-013</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -7188,19 +7188,19 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="H41" t="n">
-        <v>3026.097809356639</v>
+        <v>3007.507809356639</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-026</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -7234,19 +7234,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="H42" t="n">
-        <v>3755.055649755144</v>
+        <v>3736.465649755144</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-019</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7280,19 +7280,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2102.64</v>
+        <v>2084.05</v>
       </c>
       <c r="H43" t="n">
-        <v>5443.59246446922</v>
+        <v>5550.5346802819</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-012</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -7326,19 +7326,19 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3026.099</v>
+        <v>3007.509</v>
       </c>
       <c r="H44" t="n">
-        <v>6638.28696700587</v>
+        <v>6619.69696700587</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-011</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -7372,19 +7372,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>5352.881</v>
+        <v>3840.745</v>
       </c>
       <c r="H45" t="n">
-        <v>9270.623523772556</v>
+        <v>7606.718926283403</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7414,23 +7414,23 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>K3-G2-B-BAT-03</t>
+          <t>K3-G2-B-BAT-04</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>5443.594</v>
+        <v>4869.153</v>
       </c>
       <c r="H46" t="n">
-        <v>9209.567926283402</v>
+        <v>8786.895523772557</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-003</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -7464,19 +7464,19 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>30.495</v>
+        <v>1560.17</v>
       </c>
       <c r="H47" t="n">
-        <v>4530.415759184022</v>
+        <v>6060.090759184022</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-021</t>
         </is>
       </c>
     </row>
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1626.17</v>
+        <v>1815.961</v>
       </c>
       <c r="H48" t="n">
-        <v>6285.291989402955</v>
+        <v>6441.860943323286</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -7556,14 +7556,14 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3642.85</v>
+        <v>3601.983</v>
       </c>
       <c r="H49" t="n">
-        <v>8739.717663171208</v>
+        <v>8602.25309044097</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -7598,23 +7598,23 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>K3-G2-C-BAT-01</t>
+          <t>K3-G2-C-BAT-04</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>4530.417</v>
+        <v>4291.262</v>
       </c>
       <c r="H50" t="n">
-        <v>9465.299509758494</v>
+        <v>9226.144509758493</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-008</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-001</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1641.642</v>
+        <v>1623.052</v>
       </c>
       <c r="H52" t="n">
-        <v>4076.105873047899</v>
+        <v>4057.515873047899</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-002</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4076.107</v>
+        <v>5742.577</v>
       </c>
       <c r="H53" t="n">
-        <v>6412.084416558292</v>
+        <v>8078.554416558292</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-017</t>
         </is>
       </c>
     </row>
@@ -7772,33 +7772,33 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>A_battery</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>K2-G1-C-BAT-01</t>
+          <t>K2-G1-A-BAT-01</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>3239.784571192919</v>
+        <v>3174.895936577519</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-009</t>
         </is>
       </c>
     </row>
@@ -7818,33 +7818,33 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>A_battery</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>K2-G1-C-BAT-02</t>
+          <t>K2-G1-A-BAT-02</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2072.308</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>5288.51014937907</v>
+        <v>3779.947033441976</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7874,23 +7874,23 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-01</t>
+          <t>K2-G1-A-BAT-03</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>32.844</v>
       </c>
       <c r="H56" t="n">
-        <v>2192.366042252357</v>
+        <v>3274.434434614842</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-024</t>
         </is>
       </c>
     </row>
@@ -7905,12 +7905,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7920,23 +7920,23 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-02</t>
+          <t>K2-G1-A-BAT-04</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1313.479</v>
       </c>
       <c r="H57" t="n">
-        <v>3779.947033441976</v>
+        <v>5390.737354551678</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-020</t>
         </is>
       </c>
     </row>
@@ -7951,12 +7951,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7966,23 +7966,23 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-03</t>
+          <t>K2-G1-A-BAT-05</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2.716</v>
+        <v>1990.41</v>
       </c>
       <c r="H58" t="n">
-        <v>3177.611936577518</v>
+        <v>5149.606026117086</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-016</t>
         </is>
       </c>
     </row>
@@ -7997,12 +7997,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -8012,23 +8012,23 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-04</t>
+          <t>K2-G1-A-BAT-06</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>36.247</v>
+        <v>2229.758</v>
       </c>
       <c r="H59" t="n">
-        <v>3277.837434614842</v>
+        <v>6323.116552585012</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-015</t>
         </is>
       </c>
     </row>
@@ -8043,12 +8043,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8058,23 +8058,23 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-05</t>
+          <t>K2-G1-A-BAT-01</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1313.479</v>
+        <v>3174.897</v>
       </c>
       <c r="H60" t="n">
-        <v>5390.737354551678</v>
+        <v>6721.949810986717</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-023</t>
         </is>
       </c>
     </row>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -8104,23 +8104,23 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-06</t>
+          <t>K2-G1-A-BAT-02</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1993.126</v>
+        <v>4000.563</v>
       </c>
       <c r="H61" t="n">
-        <v>5152.322026117086</v>
+        <v>7808.561614873621</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-007</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8150,23 +8150,23 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-01</t>
+          <t>K2-G1-A-BAT-03</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2277.287</v>
+        <v>4344.632</v>
       </c>
       <c r="H62" t="n">
-        <v>6370.645552585012</v>
+        <v>8418.803815705602</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
     </row>
@@ -8181,12 +8181,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -8196,23 +8196,23 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-03</t>
+          <t>K2-G1-A-BAT-05</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3177.613</v>
+        <v>5149.607</v>
       </c>
       <c r="H63" t="n">
-        <v>6657.343227715388</v>
+        <v>8011.704299881098</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-004</t>
         </is>
       </c>
     </row>
@@ -8227,12 +8227,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -8242,14 +8242,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-02</t>
+          <t>K2-G1-A-BAT-04</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>4311.047</v>
+        <v>5557.208</v>
       </c>
       <c r="H64" t="n">
-        <v>8385.218815705603</v>
+        <v>7546.392154794932</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
     </row>
@@ -8273,38 +8273,38 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>A_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-04</t>
+          <t>K2-G1-B-BAT-01</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>4398.57</v>
+        <v>46.776</v>
       </c>
       <c r="H65" t="n">
-        <v>7945.622810986716</v>
+        <v>3007.507809356639</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-026</t>
         </is>
       </c>
     </row>
@@ -8319,38 +8319,38 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>A_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-06</t>
+          <t>K2-G1-B-BAT-02</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>5152.323</v>
+        <v>46.776</v>
       </c>
       <c r="H66" t="n">
-        <v>8733.773213282222</v>
+        <v>3736.465649755144</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
     </row>
@@ -8365,38 +8365,38 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>A_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>K2-G2-A-BAT-05</t>
+          <t>K2-G1-B-BAT-03</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>5390.738</v>
+        <v>2084.05</v>
       </c>
       <c r="H67" t="n">
-        <v>8480.457322337608</v>
+        <v>5550.5346802819</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-012</t>
         </is>
       </c>
     </row>
@@ -8411,12 +8411,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8426,23 +8426,23 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-01</t>
+          <t>K2-G1-B-BAT-01</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>65.366</v>
+        <v>3007.509</v>
       </c>
       <c r="H68" t="n">
-        <v>3026.097809356639</v>
+        <v>6619.69696700587</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-011</t>
         </is>
       </c>
     </row>
@@ -8457,12 +8457,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8472,23 +8472,23 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-02</t>
+          <t>K2-G1-B-BAT-02</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>65.366</v>
+        <v>3840.745</v>
       </c>
       <c r="H69" t="n">
-        <v>3755.055649755144</v>
+        <v>7606.718926283403</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-006</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8503,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8518,23 +8518,23 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-03</t>
+          <t>K2-G1-B-BAT-04</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1641.642</v>
+        <v>4869.153</v>
       </c>
       <c r="H70" t="n">
-        <v>4076.105873047899</v>
+        <v>8786.895523772557</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-003</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8559,23 +8559,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-04</t>
+          <t>K2-G1-C-BAT-01</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2102.64</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>5443.59246446922</v>
+        <v>3216.20214937907</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8595,38 +8595,38 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-01</t>
+          <t>K2-G1-C-BAT-02</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3026.099</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>6638.28696700587</v>
+        <v>3239.784571192919</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-022</t>
         </is>
       </c>
     </row>
@@ -8641,38 +8641,38 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-02</t>
+          <t>K2-G1-C-BAT-03</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>4076.107</v>
+        <v>1560.17</v>
       </c>
       <c r="H73" t="n">
-        <v>6412.084416558292</v>
+        <v>6060.090759184022</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
     </row>
@@ -8687,38 +8687,38 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-03</t>
+          <t>K2-G1-C-BAT-04</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>5352.881</v>
+        <v>1815.961</v>
       </c>
       <c r="H74" t="n">
-        <v>9270.623523772556</v>
+        <v>6441.860943323286</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-025</t>
         </is>
       </c>
     </row>
@@ -8733,38 +8733,38 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>B_battery</t>
+          <t>C_battery</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>K2-G2-B-BAT-04</t>
+          <t>K2-G1-C-BAT-01</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>5443.594</v>
+        <v>3601.983</v>
       </c>
       <c r="H75" t="n">
-        <v>9209.567926283402</v>
+        <v>8602.25309044097</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
     </row>
@@ -8779,12 +8779,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8794,23 +8794,23 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>K2-G2-C-BAT-01</t>
+          <t>K2-G1-C-BAT-02</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>30.495</v>
+        <v>4291.262</v>
       </c>
       <c r="H76" t="n">
-        <v>4530.415759184022</v>
+        <v>9226.144509758493</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-008</t>
         </is>
       </c>
     </row>
@@ -8830,33 +8830,33 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>A_battery</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>K2-G2-C-BAT-02</t>
+          <t>K2-G2-A-BAT-01</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1626.17</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>6285.291989402955</v>
+        <v>2192.366042252357</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-001</t>
         </is>
       </c>
     </row>
@@ -8876,33 +8876,33 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>K2-G2-C-BAT-03</t>
+          <t>K2-G2-B-BAT-01</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>3642.85</v>
+        <v>1623.052</v>
       </c>
       <c r="H78" t="n">
-        <v>8739.717663171208</v>
+        <v>4057.515873047899</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-002</t>
         </is>
       </c>
     </row>
@@ -8922,33 +8922,33 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>C_battery</t>
+          <t>B_battery</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>K2-G2-C-BAT-01</t>
+          <t>K2-G2-B-BAT-01</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>4530.417</v>
+        <v>5742.577</v>
       </c>
       <c r="H79" t="n">
-        <v>9465.299509758494</v>
+        <v>8078.554416558292</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-017</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8985,16 +8985,16 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>3239.784571192919</v>
+        <v>3216.20214937907</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-005</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9028,19 +9028,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2072.308</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>5288.51014937907</v>
+        <v>3239.784571192919</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-022</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9077,16 +9077,16 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>3779.947033441976</v>
+        <v>3174.895936577519</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-009</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9120,19 +9120,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2.716</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>3177.611936577518</v>
+        <v>3779.947033441976</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-014</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9166,19 +9166,19 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>36.247</v>
+        <v>32.844</v>
       </c>
       <c r="H84" t="n">
-        <v>3277.837434614842</v>
+        <v>3274.434434614842</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-024</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9198,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-020</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9258,19 +9258,19 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1993.126</v>
+        <v>1990.41</v>
       </c>
       <c r="H86" t="n">
-        <v>5152.322026117086</v>
+        <v>5149.606026117086</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-016</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9304,19 +9304,19 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2277.287</v>
+        <v>2229.758</v>
       </c>
       <c r="H87" t="n">
-        <v>6370.645552585012</v>
+        <v>6323.116552585012</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-015</t>
         </is>
       </c>
     </row>
@@ -9346,18 +9346,18 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>K3-G2-A-BAT-02</t>
+          <t>K3-G2-A-BAT-01</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>3177.613</v>
+        <v>3174.897</v>
       </c>
       <c r="H88" t="n">
-        <v>6657.343227715388</v>
+        <v>6721.949810986717</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9392,23 +9392,23 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>K3-G2-A-BAT-01</t>
+          <t>K3-G2-A-BAT-02</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>4311.047</v>
+        <v>4000.563</v>
       </c>
       <c r="H89" t="n">
-        <v>8385.218815705603</v>
+        <v>7808.561614873621</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-007</t>
         </is>
       </c>
     </row>
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>4398.57</v>
+        <v>4344.632</v>
       </c>
       <c r="H90" t="n">
-        <v>7945.622810986716</v>
+        <v>8418.803815705602</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9488,19 +9488,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>5152.323</v>
+        <v>5149.607</v>
       </c>
       <c r="H91" t="n">
-        <v>8733.773213282222</v>
+        <v>8011.704299881098</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-004</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9534,19 +9534,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>5390.738</v>
+        <v>5557.208</v>
       </c>
       <c r="H92" t="n">
-        <v>8480.457322337608</v>
+        <v>7546.392154794932</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-013</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9580,19 +9580,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="H93" t="n">
-        <v>3026.097809356639</v>
+        <v>3007.507809356639</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-026</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9626,19 +9626,19 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="H94" t="n">
-        <v>3755.055649755144</v>
+        <v>3736.465649755144</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-019</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9672,19 +9672,19 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2102.64</v>
+        <v>2084.05</v>
       </c>
       <c r="H95" t="n">
-        <v>5443.59246446922</v>
+        <v>5550.5346802819</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-012</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9718,19 +9718,19 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>3026.099</v>
+        <v>3007.509</v>
       </c>
       <c r="H96" t="n">
-        <v>6638.28696700587</v>
+        <v>6619.69696700587</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Q2-026</t>
+          <t>Q2-011</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9764,19 +9764,19 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>5352.881</v>
+        <v>3840.745</v>
       </c>
       <c r="H97" t="n">
-        <v>9270.623523772556</v>
+        <v>7606.718926283403</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9806,23 +9806,23 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>K3-G2-B-BAT-03</t>
+          <t>K3-G2-B-BAT-04</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>5443.594</v>
+        <v>4869.153</v>
       </c>
       <c r="H98" t="n">
-        <v>9209.567926283402</v>
+        <v>8786.895523772557</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-003</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9856,19 +9856,19 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>30.495</v>
+        <v>1560.17</v>
       </c>
       <c r="H99" t="n">
-        <v>4530.415759184022</v>
+        <v>6060.090759184022</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-021</t>
         </is>
       </c>
     </row>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1626.17</v>
+        <v>1815.961</v>
       </c>
       <c r="H100" t="n">
-        <v>6285.291989402955</v>
+        <v>6441.860943323286</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -9948,14 +9948,14 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>3642.85</v>
+        <v>3601.983</v>
       </c>
       <c r="H101" t="n">
-        <v>8739.717663171208</v>
+        <v>8602.25309044097</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9990,23 +9990,23 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>K3-G2-C-BAT-01</t>
+          <t>K3-G2-C-BAT-04</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>4530.417</v>
+        <v>4291.262</v>
       </c>
       <c r="H102" t="n">
-        <v>9465.299509758494</v>
+        <v>9226.144509758493</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-008</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-001</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10086,19 +10086,19 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1641.642</v>
+        <v>1623.052</v>
       </c>
       <c r="H104" t="n">
-        <v>4076.105873047899</v>
+        <v>4057.515873047899</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-002</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10132,10 +10132,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>4076.107</v>
+        <v>5742.577</v>
       </c>
       <c r="H105" t="n">
-        <v>6412.084416558292</v>
+        <v>8078.554416558292</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-017</t>
         </is>
       </c>
     </row>
@@ -10160,7 +10160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -10253,14 +10253,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-01</t>
+          <t>K2-G1-R-U-01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>81.00344048954707</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="H2" t="n">
-        <v>2804.206487773799</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10299,14 +10299,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-02</t>
+          <t>K2-G1-R-U-02</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="H3" t="n">
-        <v>4472.397987116188</v>
+        <v>4424.868987116189</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10345,14 +10345,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-01</t>
+          <t>K2-G1-R-U-01</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="H4" t="n">
-        <v>6021.741911727985</v>
+        <v>6410.943898832808</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10391,14 +10391,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-02</t>
+          <t>K2-G1-R-U-02</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4479.752893111123</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="H5" t="n">
-        <v>7614.782356990602</v>
+        <v>7275.244356990602</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -10422,12 +10422,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K3-G2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -10437,14 +10437,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-01</t>
+          <t>K3-G2-R-U-01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6145.052240382385</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="H6" t="n">
-        <v>7621.108589166768</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10483,23 +10483,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>K3-G2-R-U-01</t>
+          <t>K3-G2-R-U-02</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>81.00344048954707</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="H7" t="n">
-        <v>2804.206487773799</v>
+        <v>4424.868987116189</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -10529,23 +10529,23 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>K3-G2-R-U-02</t>
+          <t>K3-G2-R-U-01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>109.8448991956604</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="H8" t="n">
-        <v>4472.397987116188</v>
+        <v>6410.943898832808</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10575,43 +10575,43 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>K3-G2-R-U-01</t>
+          <t>K3-G2-R-U-02</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2882.501177057822</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="H9" t="n">
-        <v>6021.741911727985</v>
+        <v>7275.244356990602</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>strict_no_duplication</t>
+          <t>replicate_relay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K3-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>K2-G1-Q3-R01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -10621,43 +10621,43 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>K3-G2-R-U-02</t>
+          <t>K2-G1-R-U-01</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4479.752893111123</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="H10" t="n">
-        <v>7614.782356990602</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>strict_no_duplication</t>
+          <t>replicate_relay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K3-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>K2-G1-Q3-R02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -10667,23 +10667,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>K3-G2-R-U-01</t>
+          <t>K2-G1-R-U-02</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6145.052240382385</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="H11" t="n">
-        <v>7621.108589166768</v>
+        <v>4424.868987116189</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -10698,12 +10698,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R01</t>
+          <t>K2-G1-Q3-R03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10713,14 +10713,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-01</t>
+          <t>K2-G1-R-U-01</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>81.00344048954707</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="H12" t="n">
-        <v>2804.206487773799</v>
+        <v>6410.943898832808</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R02</t>
+          <t>K2-G1-Q3-R04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -10759,14 +10759,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-02</t>
+          <t>K2-G1-R-U-02</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>109.8448991956604</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="H13" t="n">
-        <v>4472.397987116188</v>
+        <v>7275.244356990602</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -10775,13 +10775,13 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10790,12 +10790,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K3-G2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R03</t>
+          <t>K3-G2-Q3-R01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10805,14 +10805,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-01</t>
+          <t>K3-G2-R-U-01</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2882.501177057822</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="H14" t="n">
-        <v>6021.741911727985</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -10821,13 +10821,13 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10836,12 +10836,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K3-G2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R04</t>
+          <t>K3-G2-Q3-R02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10851,14 +10851,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-02</t>
+          <t>K3-G2-R-U-02</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4479.752893111123</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="H15" t="n">
-        <v>7614.782356990602</v>
+        <v>4424.868987116189</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -10867,13 +10867,13 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10882,12 +10882,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K3-G2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R05</t>
+          <t>K3-G2-Q3-R03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10897,14 +10897,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>K2-G2-R-U-01</t>
+          <t>K3-G2-R-U-01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6145.052240382385</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="H16" t="n">
-        <v>7621.108589166768</v>
+        <v>6410.943898832808</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>K3-G2-Q3-R01</t>
+          <t>K3-G2-Q3-R04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10943,212 +10943,28 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>K3-G2-R-U-01</t>
+          <t>K3-G2-R-U-02</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>81.00344048954707</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="H17" t="n">
-        <v>2804.206487773799</v>
+        <v>7275.244356990602</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>replicate_relay</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K3-G2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>K3-G2-Q3-R02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>relay_UAV</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>K3-G2-R-U-02</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>109.8448991956604</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4472.397987116188</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>replicate_relay</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>K3-G2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>K3-G2-Q3-R03</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>relay_UAV</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>K3-G2-R-U-01</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>2882.501177057822</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6021.741911727985</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>replicate_relay</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>K3-G2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>K3-G2-Q3-R04</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>relay_UAV</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>K3-G2-R-U-02</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>4479.752893111123</v>
-      </c>
-      <c r="H20" t="n">
-        <v>7614.782356990602</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
           <t>Q3-R04</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>replicate_relay</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>K3-G2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>K3-G2-Q3-R05</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>relay_UAV</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>K3-G2-R-U-01</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>6145.052240382385</v>
-      </c>
-      <c r="H21" t="n">
-        <v>7621.108589166768</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11159,7 +10975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11237,7 +11053,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -11252,18 +11068,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-01</t>
+          <t>K2-G1-R-COMP-01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>81.00344048954707</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="H2" t="n">
-        <v>3261.158915271382</v>
+        <v>3263.170102771382</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>R-COMP-01</t>
+          <t>R-COMP-06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -11283,7 +11099,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11298,18 +11114,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-02</t>
+          <t>K2-G1-R-COMP-02</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="H3" t="n">
-        <v>5137.740464396822</v>
+        <v>5084.664504327378</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R-COMP-02</t>
+          <t>R-COMP-05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -11329,7 +11145,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11344,14 +11160,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-03</t>
+          <t>K2-G1-R-COMP-03</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="H4" t="n">
-        <v>6537.907948221689</v>
+        <v>6986.743725394015</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -11375,7 +11191,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11390,14 +11206,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-01</t>
+          <t>K2-G1-R-COMP-01</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4479.752893111123</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="H5" t="n">
-        <v>8126.705021376672</v>
+        <v>7740.819504883616</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -11412,7 +11228,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -11421,12 +11237,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K3-G2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -11436,23 +11252,23 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-02</t>
+          <t>K3-G2-R-COMP-01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6145.052240382385</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="H6" t="n">
-        <v>7864.247455613673</v>
+        <v>3263.170102771382</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>R-COMP-05</t>
+          <t>R-COMP-06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11288,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -11482,23 +11298,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>K3-G2-R-COMP-01</t>
+          <t>K3-G2-R-COMP-02</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>81.00344048954707</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="H7" t="n">
-        <v>3261.158915271382</v>
+        <v>5084.664504327378</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>R-COMP-01</t>
+          <t>R-COMP-05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11334,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -11528,23 +11344,23 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>K3-G2-R-COMP-02</t>
+          <t>K3-G2-R-COMP-03</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>109.8448991956604</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="H8" t="n">
-        <v>5137.740464396822</v>
+        <v>6986.743725394015</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>R-COMP-02</t>
+          <t>R-COMP-03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11380,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -11574,43 +11390,43 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>K3-G2-R-COMP-03</t>
+          <t>K3-G2-R-COMP-01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2882.501177057822</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="H9" t="n">
-        <v>6537.907948221689</v>
+        <v>7740.819504883616</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>R-COMP-03</t>
+          <t>R-COMP-04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>strict_no_duplication</t>
+          <t>replicate_relay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K3-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>K2-G1-Q3-R01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -11620,43 +11436,43 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>K3-G2-R-COMP-01</t>
+          <t>K2-G1-R-COMP-01</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4479.752893111123</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="H10" t="n">
-        <v>8126.705021376672</v>
+        <v>3263.170102771382</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>R-COMP-04</t>
+          <t>R-COMP-06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>strict_no_duplication</t>
+          <t>replicate_relay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K3-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>K2-G1-Q3-R02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -11666,14 +11482,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>K3-G2-R-COMP-02</t>
+          <t>K2-G1-R-COMP-02</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6145.052240382385</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="H11" t="n">
-        <v>7864.247455613673</v>
+        <v>5084.664504327378</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -11682,7 +11498,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -11697,12 +11513,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R01</t>
+          <t>K2-G1-Q3-R03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -11712,23 +11528,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-01</t>
+          <t>K2-G1-R-COMP-03</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>81.00344048954707</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="H12" t="n">
-        <v>3261.158915271382</v>
+        <v>6986.743725394015</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>R-COMP-01</t>
+          <t>R-COMP-03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -11743,12 +11559,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R02</t>
+          <t>K2-G1-Q3-R04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -11758,29 +11574,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-02</t>
+          <t>K2-G1-R-COMP-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>109.8448991956604</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="H13" t="n">
-        <v>5137.740464396822</v>
+        <v>7740.819504883616</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>R-COMP-02</t>
+          <t>R-COMP-04</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -11789,12 +11605,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K3-G2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R03</t>
+          <t>K3-G2-Q3-R01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -11804,29 +11620,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-03</t>
+          <t>K3-G2-R-COMP-01</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2882.501177057822</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="H14" t="n">
-        <v>6537.907948221689</v>
+        <v>3263.170102771382</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>R-COMP-03</t>
+          <t>R-COMP-06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -11835,12 +11651,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K3-G2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R04</t>
+          <t>K3-G2-Q3-R02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -11850,29 +11666,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-01</t>
+          <t>K3-G2-R-COMP-02</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4479.752893111123</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="H15" t="n">
-        <v>8126.705021376672</v>
+        <v>5084.664504327378</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>R-COMP-04</t>
+          <t>R-COMP-05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -11881,12 +11697,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K3-G2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R05</t>
+          <t>K3-G2-Q3-R03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -11896,23 +11712,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>K2-G2-R-COMP-02</t>
+          <t>K3-G2-R-COMP-03</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6145.052240382385</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="H16" t="n">
-        <v>7864.247455613673</v>
+        <v>6986.743725394015</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>R-COMP-05</t>
+          <t>R-COMP-03</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11748,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>K3-G2-Q3-R01</t>
+          <t>K3-G2-Q3-R04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -11946,208 +11762,24 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>81.00344048954707</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="H17" t="n">
-        <v>3261.158915271382</v>
+        <v>7740.819504883616</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>R-COMP-01</t>
+          <t>R-COMP-04</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>replicate_relay</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K3-G2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>K3-G2-Q3-R02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>relay_component</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>K3-G2-R-COMP-02</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>109.8448991956604</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5137.740464396822</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>R-COMP-02</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>replicate_relay</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>K3-G2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>K3-G2-Q3-R03</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>relay_component</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>K3-G2-R-COMP-03</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>2882.501177057822</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6537.907948221689</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>R-COMP-03</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>replicate_relay</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>K3-G2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>K3-G2-Q3-R04</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>relay_component</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>K3-G2-R-COMP-01</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>4479.752893111123</v>
-      </c>
-      <c r="H20" t="n">
-        <v>8126.705021376672</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>R-COMP-04</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
           <t>Q3-R04</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>replicate_relay</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>K3-G2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>K3-G2-Q3-R05</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>relay_component</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>K3-G2-R-COMP-02</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>6145.052240382385</v>
-      </c>
-      <c r="H21" t="n">
-        <v>7864.247455613673</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>R-COMP-05</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>